--- a/VerveStacks_ETH_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ETH_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ETH_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2E9B5C7-07CB-4E5E-A1DD-1DC7AC7F3A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{294CDF03-1B50-4A0D-B0FB-8C876630A877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1050,18 +1050,108 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ETH_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ETH_020</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ETH_025</t>
   </si>
   <si>
@@ -1080,162 +1170,126 @@
     <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ETH_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ETH_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ETH_021</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ETH_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ETH_018</t>
   </si>
   <si>
@@ -1254,66 +1308,54 @@
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ETH_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ETH_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w569990174-500_ETH</t>
+  </si>
+  <si>
+    <t>e_w569627610-400_ETH,e_ET19-230_ETH</t>
+  </si>
+  <si>
+    <t>e_w695773621-230_ETH,e_w220122466-230_ETH,e_w180619166-230_ETH</t>
+  </si>
+  <si>
+    <t>e_w222891421-230_ETH,e_w576081254-400_ETH</t>
+  </si>
+  <si>
+    <t>e_w422547473-230_ETH</t>
+  </si>
+  <si>
+    <t>e_w186395768-230_ETH,e_w576081254-400_ETH,e_w220122466-230_ETH,e_w695773621-230_ETH</t>
+  </si>
+  <si>
+    <t>e_w222891421-230_ETH</t>
+  </si>
+  <si>
+    <t>e_w569627610-400_ETH,e_w222891421-230_ETH,e_w576081254-400_ETH</t>
+  </si>
+  <si>
+    <t>e_w670304976-230_ETH,e_w422547473-230_ETH</t>
+  </si>
+  <si>
+    <t>e_w670304976-230_ETH</t>
+  </si>
+  <si>
+    <t>e_w569627610-400_ETH</t>
+  </si>
+  <si>
+    <t>e_w859755774-500_ETH,e_w220122466-230_ETH,e_w186395768-230_ETH</t>
+  </si>
+  <si>
+    <t>e_w180619166-230_ETH</t>
+  </si>
+  <si>
+    <t>e_w695773621-230_ETH,e_w422547473-230_ETH</t>
+  </si>
+  <si>
     <t>e_w859755774-500_ETH,e_w569990174-500_ETH</t>
   </si>
   <si>
@@ -1323,79 +1365,127 @@
     <t>e_w569627610-400_ETH,e_w222891421-230_ETH</t>
   </si>
   <si>
-    <t>e_w670304976-230_ETH</t>
+    <t>e_w569990174-500_ETH,e_w569627610-400_ETH</t>
+  </si>
+  <si>
+    <t>e_ET19-230_ETH,e_w569627610-400_ETH,e_w576081254-400_ETH</t>
+  </si>
+  <si>
+    <t>e_w180619166-230_ETH,e_w695773621-230_ETH</t>
+  </si>
+  <si>
+    <t>e_w422547473-230_ETH,e_w695773621-230_ETH,e_w180619166-230_ETH</t>
+  </si>
+  <si>
+    <t>e_w220122466-230_ETH,e_ET2-230_ETH</t>
+  </si>
+  <si>
+    <t>e_w576081254-400_ETH,e_w422547473-230_ETH</t>
+  </si>
+  <si>
+    <t>e_w222891421-230_ETH,e_w670304976-230_ETH</t>
+  </si>
+  <si>
+    <t>e_w220122466-230_ETH,e_w180619166-230_ETH</t>
+  </si>
+  <si>
+    <t>e_w222891421-230_ETH,e_w422547473-230_ETH,e_w670304976-230_ETH</t>
   </si>
   <si>
     <t>e_w569990174-500_ETH,e_w186395768-230_ETH</t>
   </si>
   <si>
-    <t>e_w222891421-230_ETH</t>
-  </si>
-  <si>
-    <t>e_w569627610-400_ETH</t>
-  </si>
-  <si>
-    <t>e_w220122466-230_ETH,e_w180619166-230_ETH</t>
-  </si>
-  <si>
-    <t>e_w569990174-500_ETH,e_w569627610-400_ETH</t>
-  </si>
-  <si>
-    <t>e_w422547473-230_ETH</t>
-  </si>
-  <si>
-    <t>e_w569990174-500_ETH</t>
-  </si>
-  <si>
-    <t>e_w569627610-400_ETH,e_ET19-230_ETH</t>
-  </si>
-  <si>
-    <t>e_w222891421-230_ETH,e_w422547473-230_ETH,e_w670304976-230_ETH</t>
-  </si>
-  <si>
-    <t>e_w695773621-230_ETH,e_w220122466-230_ETH,e_w180619166-230_ETH</t>
-  </si>
-  <si>
-    <t>e_w222891421-230_ETH,e_w576081254-400_ETH</t>
-  </si>
-  <si>
-    <t>e_w220122466-230_ETH,e_ET2-230_ETH</t>
-  </si>
-  <si>
-    <t>e_w576081254-400_ETH,e_w422547473-230_ETH</t>
-  </si>
-  <si>
-    <t>e_w222891421-230_ETH,e_w670304976-230_ETH</t>
-  </si>
-  <si>
-    <t>e_w695773621-230_ETH,e_w422547473-230_ETH</t>
-  </si>
-  <si>
-    <t>e_w859755774-500_ETH,e_w220122466-230_ETH,e_w186395768-230_ETH</t>
-  </si>
-  <si>
-    <t>e_w180619166-230_ETH</t>
-  </si>
-  <si>
     <t>e_w222891421-230_ETH,e_w422547473-230_ETH</t>
   </si>
   <si>
-    <t>e_w186395768-230_ETH,e_w576081254-400_ETH,e_w220122466-230_ETH,e_w695773621-230_ETH</t>
-  </si>
-  <si>
-    <t>e_w569627610-400_ETH,e_w222891421-230_ETH,e_w576081254-400_ETH</t>
-  </si>
-  <si>
-    <t>e_w670304976-230_ETH,e_w422547473-230_ETH</t>
-  </si>
-  <si>
-    <t>e_ET19-230_ETH,e_w569627610-400_ETH,e_w576081254-400_ETH</t>
-  </si>
-  <si>
-    <t>e_w180619166-230_ETH,e_w695773621-230_ETH</t>
-  </si>
-  <si>
-    <t>e_w422547473-230_ETH,e_w695773621-230_ETH,e_w180619166-230_ETH</t>
+    <t>distr_wonelc_won_ETH_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
   </si>
   <si>
     <t>distr_wonelc_won_ETH_017</t>
@@ -1404,6 +1494,24 @@
     <t>connecting wind onshore to buses in cluster 17</t>
   </si>
   <si>
+    <t>distr_wonelc_won_ETH_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_ETH_001</t>
   </si>
   <si>
@@ -1416,142 +1524,97 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
+    <t>distr_wonelc_won_ETH_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ETH_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_ETH_013</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ETH_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ETH_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
+    <t>elc_won_ETH_008</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_006</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_021</t>
+  </si>
+  <si>
+    <t>e_w859755774-500_ETH</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_014</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_015</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_003</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_022</t>
+  </si>
+  <si>
+    <t>e_w859755774-500_ETH,e_w220122466-230_ETH,e_ET2-230_ETH</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_020</t>
+  </si>
+  <si>
+    <t>e_ET2-230_ETH</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_023</t>
+  </si>
+  <si>
+    <t>e_w569627610-400_ETH,e_w576081254-400_ETH</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_025</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_011</t>
+  </si>
+  <si>
+    <t>e_w422547473-230_ETH,e_w670304976-230_ETH</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_010</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_004</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_007</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_026</t>
+  </si>
+  <si>
+    <t>e_w422547473-230_ETH,e_w695773621-230_ETH</t>
   </si>
   <si>
     <t>elc_won_ETH_017</t>
@@ -1560,100 +1623,37 @@
     <t>e_w695773621-230_ETH,e_w180619166-230_ETH</t>
   </si>
   <si>
+    <t>elc_won_ETH_018</t>
+  </si>
+  <si>
+    <t>e_w695773621-230_ETH</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_019</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_024</t>
+  </si>
+  <si>
     <t>elc_won_ETH_001</t>
   </si>
   <si>
     <t>elc_won_ETH_012</t>
   </si>
   <si>
+    <t>elc_won_ETH_002</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_009</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_016</t>
+  </si>
+  <si>
+    <t>elc_won_ETH_005</t>
+  </si>
+  <si>
     <t>elc_won_ETH_013</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_024</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_010</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_004</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_003</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_022</t>
-  </si>
-  <si>
-    <t>e_w859755774-500_ETH,e_w220122466-230_ETH,e_ET2-230_ETH</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_020</t>
-  </si>
-  <si>
-    <t>e_ET2-230_ETH</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_009</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_016</t>
-  </si>
-  <si>
-    <t>e_w695773621-230_ETH</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_005</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_015</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_007</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_026</t>
-  </si>
-  <si>
-    <t>e_w422547473-230_ETH,e_w695773621-230_ETH</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_008</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_006</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_002</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_018</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_019</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_023</t>
-  </si>
-  <si>
-    <t>e_w569627610-400_ETH,e_w576081254-400_ETH</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_025</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_011</t>
-  </si>
-  <si>
-    <t>e_w422547473-230_ETH,e_w670304976-230_ETH</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_021</t>
-  </si>
-  <si>
-    <t>e_w859755774-500_ETH</t>
-  </si>
-  <si>
-    <t>elc_won_ETH_014</t>
   </si>
   <si>
     <t>e_won_ETH_001</t>
@@ -6637,7 +6637,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63371E3B-7E30-4BCB-BDAF-C940BD102B64}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4405BD72-9B3A-4C8B-A09F-86BF8A15A216}">
   <dimension ref="B9:AP52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6833,16 +6833,16 @@
         <v>307</v>
       </c>
       <c r="Y11" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Z11" t="s">
         <v>395</v>
       </c>
       <c r="AA11">
-        <v>0.995251433314843</v>
+        <v>0.99253042581653972</v>
       </c>
       <c r="AB11">
-        <v>87.057055894544277</v>
+        <v>136.94219336343826</v>
       </c>
       <c r="AD11" t="s">
         <v>306</v>
@@ -6872,13 +6872,13 @@
         <v>475</v>
       </c>
       <c r="AN11" t="s">
-        <v>476</v>
+        <v>418</v>
       </c>
       <c r="AO11">
-        <v>0.99486776831099377</v>
+        <v>0.99596696920956196</v>
       </c>
       <c r="AP11">
-        <v>94.090914298447927</v>
+        <v>73.938897824697335</v>
       </c>
     </row>
     <row r="12" spans="2:42">
@@ -6943,16 +6943,16 @@
         <v>311</v>
       </c>
       <c r="Y12" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="Z12" t="s">
         <v>396</v>
       </c>
       <c r="AA12">
-        <v>0.99671843931109627</v>
+        <v>0.99796858573578295</v>
       </c>
       <c r="AB12">
-        <v>60.16194596323551</v>
+        <v>37.242594843978267</v>
       </c>
       <c r="AD12" t="s">
         <v>306</v>
@@ -6979,16 +6979,16 @@
         <v>425</v>
       </c>
       <c r="AM12" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AN12" t="s">
-        <v>397</v>
+        <v>420</v>
       </c>
       <c r="AO12">
-        <v>0.98585787484342058</v>
+        <v>0.99006862546840091</v>
       </c>
       <c r="AP12">
-        <v>259.27229453729018</v>
+        <v>182.07519974598432</v>
       </c>
     </row>
     <row r="13" spans="2:42">
@@ -7053,16 +7053,16 @@
         <v>313</v>
       </c>
       <c r="Y13" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="Z13" t="s">
         <v>397</v>
       </c>
       <c r="AA13">
-        <v>0.98572590028571305</v>
+        <v>0.99843163451607075</v>
       </c>
       <c r="AB13">
-        <v>261.6918280952612</v>
+        <v>28.753367205370328</v>
       </c>
       <c r="AD13" t="s">
         <v>306</v>
@@ -7089,16 +7089,16 @@
         <v>427</v>
       </c>
       <c r="AM13" t="s">
+        <v>477</v>
+      </c>
+      <c r="AN13" t="s">
         <v>478</v>
       </c>
-      <c r="AN13" t="s">
-        <v>398</v>
-      </c>
       <c r="AO13">
-        <v>0.980829980955647</v>
+        <v>0.99426720646313538</v>
       </c>
       <c r="AP13">
-        <v>351.45034914647096</v>
+        <v>105.1012148425182</v>
       </c>
     </row>
     <row r="14" spans="2:42">
@@ -7163,16 +7163,16 @@
         <v>315</v>
       </c>
       <c r="Y14" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
       <c r="Z14" t="s">
         <v>398</v>
       </c>
       <c r="AA14">
-        <v>0.98259551601550377</v>
+        <v>0.99532983360173577</v>
       </c>
       <c r="AB14">
-        <v>319.08220638243114</v>
+        <v>85.619717301511258</v>
       </c>
       <c r="AD14" t="s">
         <v>306</v>
@@ -7202,13 +7202,13 @@
         <v>479</v>
       </c>
       <c r="AN14" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="AO14">
-        <v>0.99247535827987554</v>
+        <v>0.9906119561243919</v>
       </c>
       <c r="AP14">
-        <v>137.95176486894792</v>
+        <v>172.11413771948116</v>
       </c>
     </row>
     <row r="15" spans="2:42">
@@ -7273,16 +7273,16 @@
         <v>317</v>
       </c>
       <c r="Y15" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="Z15" t="s">
         <v>399</v>
       </c>
       <c r="AA15">
-        <v>0.99732773592901214</v>
+        <v>0.99511057711952233</v>
       </c>
       <c r="AB15">
-        <v>48.991507968111527</v>
+        <v>89.639419475423097</v>
       </c>
       <c r="AD15" t="s">
         <v>306</v>
@@ -7312,13 +7312,13 @@
         <v>480</v>
       </c>
       <c r="AN15" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="AO15">
-        <v>0.9975926286565272</v>
+        <v>0.99658842129154079</v>
       </c>
       <c r="AP15">
-        <v>44.135141297001994</v>
+        <v>62.545609655086125</v>
       </c>
     </row>
     <row r="16" spans="2:42">
@@ -7383,16 +7383,16 @@
         <v>319</v>
       </c>
       <c r="Y16" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="Z16" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="AA16">
-        <v>0.99561529276418437</v>
+        <v>0.99475942890752744</v>
       </c>
       <c r="AB16">
-        <v>80.386299323287233</v>
+        <v>96.077136695329571</v>
       </c>
       <c r="AD16" t="s">
         <v>306</v>
@@ -7422,13 +7422,13 @@
         <v>481</v>
       </c>
       <c r="AN16" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AO16">
-        <v>0.99130788322046459</v>
+        <v>0.98799922319206057</v>
       </c>
       <c r="AP16">
-        <v>159.35547429148349</v>
+        <v>220.01424147888963</v>
       </c>
     </row>
     <row r="17" spans="2:42">
@@ -7493,16 +7493,16 @@
         <v>321</v>
       </c>
       <c r="Y17" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="Z17" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AA17">
-        <v>0.98050338477759325</v>
+        <v>0.99786559838801514</v>
       </c>
       <c r="AB17">
-        <v>357.43794574412465</v>
+        <v>39.130696219723248</v>
       </c>
       <c r="AD17" t="s">
         <v>306</v>
@@ -7532,13 +7532,13 @@
         <v>482</v>
       </c>
       <c r="AN17" t="s">
-        <v>411</v>
+        <v>483</v>
       </c>
       <c r="AO17">
-        <v>0.99546374244265856</v>
+        <v>0.99509039878960082</v>
       </c>
       <c r="AP17">
-        <v>83.164721884592765</v>
+        <v>90.009355523984212</v>
       </c>
     </row>
     <row r="18" spans="2:42">
@@ -7603,16 +7603,16 @@
         <v>323</v>
       </c>
       <c r="Y18" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Z18" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA18">
-        <v>0.98970367680335103</v>
+        <v>0.99012440822560344</v>
       </c>
       <c r="AB18">
-        <v>188.76592527189771</v>
+        <v>181.05251586393737</v>
       </c>
       <c r="AD18" t="s">
         <v>306</v>
@@ -7639,16 +7639,16 @@
         <v>437</v>
       </c>
       <c r="AM18" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN18" t="s">
-        <v>401</v>
+        <v>485</v>
       </c>
       <c r="AO18">
-        <v>0.98799922319206057</v>
+        <v>0.99776689522677653</v>
       </c>
       <c r="AP18">
-        <v>220.01424147888963</v>
+        <v>40.940254175764622</v>
       </c>
     </row>
     <row r="19" spans="2:42">
@@ -7713,16 +7713,16 @@
         <v>325</v>
       </c>
       <c r="Y19" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="Z19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AA19">
-        <v>0.99136478772206271</v>
+        <v>0.99593912771817861</v>
       </c>
       <c r="AB19">
-        <v>158.312225095516</v>
+        <v>74.449325166725842</v>
       </c>
       <c r="AD19" t="s">
         <v>306</v>
@@ -7749,16 +7749,16 @@
         <v>439</v>
       </c>
       <c r="AM19" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AN19" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AO19">
-        <v>0.99509039878960082</v>
+        <v>0.99700451808909196</v>
       </c>
       <c r="AP19">
-        <v>90.009355523984212</v>
+        <v>54.917168366647161</v>
       </c>
     </row>
     <row r="20" spans="2:42">
@@ -7823,16 +7823,16 @@
         <v>327</v>
       </c>
       <c r="Y20" t="s">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="Z20" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AA20">
-        <v>0.99698686127496883</v>
+        <v>0.99002892693938738</v>
       </c>
       <c r="AB20">
-        <v>55.240876625571026</v>
+        <v>182.80300611123195</v>
       </c>
       <c r="AD20" t="s">
         <v>306</v>
@@ -7859,16 +7859,16 @@
         <v>441</v>
       </c>
       <c r="AM20" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AN20" t="s">
-        <v>487</v>
+        <v>399</v>
       </c>
       <c r="AO20">
-        <v>0.99776689522677653</v>
+        <v>0.99714901331742301</v>
       </c>
       <c r="AP20">
-        <v>40.940254175764622</v>
+        <v>52.268089180578727</v>
       </c>
     </row>
     <row r="21" spans="2:42">
@@ -7933,16 +7933,16 @@
         <v>329</v>
       </c>
       <c r="Y21" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="Z21" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AA21">
-        <v>0.98948525265458209</v>
+        <v>0.98656930418149524</v>
       </c>
       <c r="AB21">
-        <v>192.77036799932733</v>
+        <v>246.22942333925477</v>
       </c>
       <c r="AD21" t="s">
         <v>306</v>
@@ -7969,16 +7969,16 @@
         <v>443</v>
       </c>
       <c r="AM21" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AN21" t="s">
-        <v>400</v>
+        <v>490</v>
       </c>
       <c r="AO21">
-        <v>0.99528345302339694</v>
+        <v>0.98351541785442109</v>
       </c>
       <c r="AP21">
-        <v>86.470027904389667</v>
+        <v>302.21733933561291</v>
       </c>
     </row>
     <row r="22" spans="2:42">
@@ -8043,16 +8043,16 @@
         <v>331</v>
       </c>
       <c r="Y22" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="Z22" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="AA22">
-        <v>0.99411318037218566</v>
+        <v>0.99525906207419357</v>
       </c>
       <c r="AB22">
-        <v>107.92502650993045</v>
+        <v>86.917195306450438</v>
       </c>
       <c r="AD22" t="s">
         <v>306</v>
@@ -8079,16 +8079,16 @@
         <v>445</v>
       </c>
       <c r="AM22" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AN22" t="s">
-        <v>490</v>
+        <v>401</v>
       </c>
       <c r="AO22">
-        <v>0.99833166764916648</v>
+        <v>0.99130788322046459</v>
       </c>
       <c r="AP22">
-        <v>30.58609309861421</v>
+        <v>159.35547429148349</v>
       </c>
     </row>
     <row r="23" spans="2:42">
@@ -8153,16 +8153,16 @@
         <v>333</v>
       </c>
       <c r="Y23" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="Z23" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AA23">
-        <v>0.98843399793171816</v>
+        <v>0.99661017746506597</v>
       </c>
       <c r="AB23">
-        <v>212.04337125183315</v>
+        <v>62.14674647379104</v>
       </c>
       <c r="AD23" t="s">
         <v>306</v>
@@ -8189,16 +8189,16 @@
         <v>447</v>
       </c>
       <c r="AM23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AN23" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="AO23">
-        <v>0.99283514087698799</v>
+        <v>0.99546374244265856</v>
       </c>
       <c r="AP23">
-        <v>131.35575058855423</v>
+        <v>83.164721884592765</v>
       </c>
     </row>
     <row r="24" spans="2:42">
@@ -8263,16 +8263,16 @@
         <v>335</v>
       </c>
       <c r="Y24" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="Z24" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="AA24">
-        <v>0.99245733785731916</v>
+        <v>0.99746762516641851</v>
       </c>
       <c r="AB24">
-        <v>138.28213928248309</v>
+        <v>46.426871948993622</v>
       </c>
       <c r="AD24" t="s">
         <v>306</v>
@@ -8299,16 +8299,16 @@
         <v>449</v>
       </c>
       <c r="AM24" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN24" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="AO24">
-        <v>0.99658842129154079</v>
+        <v>0.99531675893352978</v>
       </c>
       <c r="AP24">
-        <v>62.545609655086125</v>
+        <v>85.859419551954957</v>
       </c>
     </row>
     <row r="25" spans="2:42">
@@ -8373,16 +8373,16 @@
         <v>337</v>
       </c>
       <c r="Y25" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Z25" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AA25">
-        <v>0.99253042581653972</v>
+        <v>0.99611797788526413</v>
       </c>
       <c r="AB25">
-        <v>136.94219336343826</v>
+        <v>71.170405436823458</v>
       </c>
       <c r="AD25" t="s">
         <v>306</v>
@@ -8409,16 +8409,16 @@
         <v>451</v>
       </c>
       <c r="AM25" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AN25" t="s">
-        <v>416</v>
+        <v>495</v>
       </c>
       <c r="AO25">
-        <v>0.99531675893352978</v>
+        <v>0.99435288717102477</v>
       </c>
       <c r="AP25">
-        <v>85.859419551954957</v>
+        <v>103.53040186454626</v>
       </c>
     </row>
     <row r="26" spans="2:42">
@@ -8483,16 +8483,16 @@
         <v>339</v>
       </c>
       <c r="Y26" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="Z26" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AA26">
-        <v>0.99796858573578295</v>
+        <v>0.995251433314843</v>
       </c>
       <c r="AB26">
-        <v>37.242594843978267</v>
+        <v>87.057055894544277</v>
       </c>
       <c r="AD26" t="s">
         <v>306</v>
@@ -8519,16 +8519,16 @@
         <v>453</v>
       </c>
       <c r="AM26" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="AN26" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AO26">
-        <v>0.99435288717102477</v>
+        <v>0.99486776831099377</v>
       </c>
       <c r="AP26">
-        <v>103.53040186454626</v>
+        <v>94.090914298447927</v>
       </c>
     </row>
     <row r="27" spans="2:42">
@@ -8593,16 +8593,16 @@
         <v>341</v>
       </c>
       <c r="Y27" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Z27" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="AA27">
-        <v>0.99376440697670854</v>
+        <v>0.99671843931109627</v>
       </c>
       <c r="AB27">
-        <v>114.31920542701046</v>
+        <v>60.16194596323551</v>
       </c>
       <c r="AD27" t="s">
         <v>306</v>
@@ -8629,16 +8629,16 @@
         <v>455</v>
       </c>
       <c r="AM27" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AN27" t="s">
-        <v>412</v>
+        <v>499</v>
       </c>
       <c r="AO27">
-        <v>0.99596696920956196</v>
+        <v>0.99638628734094292</v>
       </c>
       <c r="AP27">
-        <v>73.938897824697335</v>
+        <v>66.251398749380073</v>
       </c>
     </row>
     <row r="28" spans="2:42">
@@ -8703,16 +8703,16 @@
         <v>343</v>
       </c>
       <c r="Y28" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Z28" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="AA28">
-        <v>0.98955368335535221</v>
+        <v>0.98572590028571305</v>
       </c>
       <c r="AB28">
-        <v>191.51580515187584</v>
+        <v>261.6918280952612</v>
       </c>
       <c r="AD28" t="s">
         <v>306</v>
@@ -8739,16 +8739,16 @@
         <v>457</v>
       </c>
       <c r="AM28" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AN28" t="s">
         <v>407</v>
       </c>
       <c r="AO28">
-        <v>0.99006862546840091</v>
+        <v>0.99661464463851446</v>
       </c>
       <c r="AP28">
-        <v>182.07519974598432</v>
+        <v>62.064848293900809</v>
       </c>
     </row>
     <row r="29" spans="2:42">
@@ -8813,16 +8813,16 @@
         <v>345</v>
       </c>
       <c r="Y29" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Z29" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="AA29">
-        <v>0.99310639001954748</v>
+        <v>0.98259551601550377</v>
       </c>
       <c r="AB29">
-        <v>126.38284964163027</v>
+        <v>319.08220638243114</v>
       </c>
       <c r="AD29" t="s">
         <v>306</v>
@@ -8849,16 +8849,16 @@
         <v>459</v>
       </c>
       <c r="AM29" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AN29" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="AO29">
-        <v>0.98807695887980829</v>
+        <v>0.9975926286565272</v>
       </c>
       <c r="AP29">
-        <v>218.58908720351531</v>
+        <v>44.135141297001994</v>
       </c>
     </row>
     <row r="30" spans="2:42">
@@ -8923,16 +8923,16 @@
         <v>347</v>
       </c>
       <c r="Y30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Z30" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="AA30">
-        <v>0.99843163451607075</v>
+        <v>0.98948525265458209</v>
       </c>
       <c r="AB30">
-        <v>28.753367205370328</v>
+        <v>192.77036799932733</v>
       </c>
       <c r="AD30" t="s">
         <v>306</v>
@@ -8959,16 +8959,16 @@
         <v>461</v>
       </c>
       <c r="AM30" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AN30" t="s">
-        <v>490</v>
+        <v>411</v>
       </c>
       <c r="AO30">
-        <v>0.99638628734094292</v>
+        <v>0.98585787484342058</v>
       </c>
       <c r="AP30">
-        <v>66.251398749380073</v>
+        <v>259.27229453729018</v>
       </c>
     </row>
     <row r="31" spans="2:42">
@@ -9033,16 +9033,16 @@
         <v>349</v>
       </c>
       <c r="Y31" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="Z31" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="AA31">
-        <v>0.99532983360173577</v>
+        <v>0.99411318037218566</v>
       </c>
       <c r="AB31">
-        <v>85.619717301511258</v>
+        <v>107.92502650993045</v>
       </c>
       <c r="AD31" t="s">
         <v>306</v>
@@ -9069,16 +9069,16 @@
         <v>463</v>
       </c>
       <c r="AM31" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AN31" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="AO31">
-        <v>0.99661464463851446</v>
+        <v>0.980829980955647</v>
       </c>
       <c r="AP31">
-        <v>62.064848293900809</v>
+        <v>351.45034914647096</v>
       </c>
     </row>
     <row r="32" spans="2:42">
@@ -9143,16 +9143,16 @@
         <v>351</v>
       </c>
       <c r="Y32" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Z32" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="AA32">
-        <v>0.99511057711952233</v>
+        <v>0.98843399793171816</v>
       </c>
       <c r="AB32">
-        <v>89.639419475423097</v>
+        <v>212.04337125183315</v>
       </c>
       <c r="AD32" t="s">
         <v>306</v>
@@ -9179,16 +9179,16 @@
         <v>465</v>
       </c>
       <c r="AM32" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AN32" t="s">
-        <v>502</v>
+        <v>405</v>
       </c>
       <c r="AO32">
-        <v>0.99700451808909196</v>
+        <v>0.98807695887980829</v>
       </c>
       <c r="AP32">
-        <v>54.917168366647161</v>
+        <v>218.58908720351531</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -9253,16 +9253,16 @@
         <v>353</v>
       </c>
       <c r="Y33" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="Z33" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="AA33">
-        <v>0.9964468080316583</v>
+        <v>0.99245733785731916</v>
       </c>
       <c r="AB33">
-        <v>65.141852752931669</v>
+        <v>138.28213928248309</v>
       </c>
       <c r="AD33" t="s">
         <v>306</v>
@@ -9289,16 +9289,16 @@
         <v>467</v>
       </c>
       <c r="AM33" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AN33" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="AO33">
-        <v>0.99714901331742301</v>
+        <v>0.99528345302339694</v>
       </c>
       <c r="AP33">
-        <v>52.268089180578727</v>
+        <v>86.470027904389667</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -9363,16 +9363,16 @@
         <v>355</v>
       </c>
       <c r="Y34" t="s">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="Z34" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="AA34">
-        <v>0.99485299083497092</v>
+        <v>0.99786910267543361</v>
       </c>
       <c r="AB34">
-        <v>94.36183469219965</v>
+        <v>39.066450950384784</v>
       </c>
       <c r="AD34" t="s">
         <v>306</v>
@@ -9399,16 +9399,16 @@
         <v>469</v>
       </c>
       <c r="AM34" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AN34" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="AO34">
-        <v>0.98351541785442109</v>
+        <v>0.99833166764916648</v>
       </c>
       <c r="AP34">
-        <v>302.21733933561291</v>
+        <v>30.58609309861421</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -9473,16 +9473,16 @@
         <v>357</v>
       </c>
       <c r="Y35" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="Z35" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AA35">
-        <v>0.99595679740127385</v>
+        <v>0.99670581568863215</v>
       </c>
       <c r="AB35">
-        <v>74.125380976645999</v>
+        <v>60.393379041744041</v>
       </c>
       <c r="AD35" t="s">
         <v>306</v>
@@ -9509,16 +9509,16 @@
         <v>471</v>
       </c>
       <c r="AM35" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AN35" t="s">
-        <v>507</v>
+        <v>399</v>
       </c>
       <c r="AO35">
-        <v>0.99426720646313538</v>
+        <v>0.99283514087698799</v>
       </c>
       <c r="AP35">
-        <v>105.1012148425182</v>
+        <v>131.35575058855423</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -9583,16 +9583,16 @@
         <v>359</v>
       </c>
       <c r="Y36" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="Z36" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AA36">
-        <v>0.98932256771504001</v>
+        <v>0.99618977432187161</v>
       </c>
       <c r="AB36">
-        <v>195.75292522426653</v>
+        <v>69.854137432352857</v>
       </c>
       <c r="AD36" t="s">
         <v>306</v>
@@ -9622,13 +9622,13 @@
         <v>508</v>
       </c>
       <c r="AN36" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="AO36">
-        <v>0.9906119561243919</v>
+        <v>0.99247535827987554</v>
       </c>
       <c r="AP36">
-        <v>172.11413771948116</v>
+        <v>137.95176486894792</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -9693,16 +9693,16 @@
         <v>361</v>
       </c>
       <c r="Y37" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="Z37" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="AA37">
-        <v>0.99611797788526413</v>
+        <v>0.99561529276418437</v>
       </c>
       <c r="AB37">
-        <v>71.170405436823458</v>
+        <v>80.386299323287233</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -9767,16 +9767,16 @@
         <v>363</v>
       </c>
       <c r="Y38" t="s">
-        <v>297</v>
+        <v>267</v>
       </c>
       <c r="Z38" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AA38">
-        <v>0.99525906207419357</v>
+        <v>0.98050338477759325</v>
       </c>
       <c r="AB38">
-        <v>86.917195306450438</v>
+        <v>357.43794574412465</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -9841,16 +9841,16 @@
         <v>365</v>
       </c>
       <c r="Y39" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z39" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AA39">
-        <v>0.99661017746506597</v>
+        <v>0.9964468080316583</v>
       </c>
       <c r="AB39">
-        <v>62.14674647379104</v>
+        <v>65.141852752931669</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -9915,16 +9915,16 @@
         <v>367</v>
       </c>
       <c r="Y40" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="Z40" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="AA40">
-        <v>0.99746762516641851</v>
+        <v>0.99485299083497092</v>
       </c>
       <c r="AB40">
-        <v>46.426871948993622</v>
+        <v>94.36183469219965</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -9989,16 +9989,16 @@
         <v>369</v>
       </c>
       <c r="Y41" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="Z41" t="s">
-        <v>400</v>
+        <v>417</v>
       </c>
       <c r="AA41">
-        <v>0.9949180004872078</v>
+        <v>0.99595679740127385</v>
       </c>
       <c r="AB41">
-        <v>93.1699910678566</v>
+        <v>74.125380976645999</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -10063,16 +10063,16 @@
         <v>371</v>
       </c>
       <c r="Y42" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Z42" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="AA42">
-        <v>0.97445949249159303</v>
+        <v>0.98932256771504001</v>
       </c>
       <c r="AB42">
-        <v>468.24263765412724</v>
+        <v>195.75292522426653</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -10137,16 +10137,16 @@
         <v>373</v>
       </c>
       <c r="Y43" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="Z43" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="AA43">
-        <v>0.99209119567036697</v>
+        <v>0.98970367680335103</v>
       </c>
       <c r="AB43">
-        <v>144.9947460432729</v>
+        <v>188.76592527189771</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -10211,16 +10211,16 @@
         <v>375</v>
       </c>
       <c r="Y44" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="Z44" t="s">
         <v>405</v>
       </c>
       <c r="AA44">
-        <v>0.99475942890752744</v>
+        <v>0.99136478772206271</v>
       </c>
       <c r="AB44">
-        <v>96.077136695329571</v>
+        <v>158.312225095516</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -10285,16 +10285,16 @@
         <v>377</v>
       </c>
       <c r="Y45" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Z45" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AA45">
-        <v>0.99786559838801514</v>
+        <v>0.99698686127496883</v>
       </c>
       <c r="AB45">
-        <v>39.130696219723248</v>
+        <v>55.240876625571026</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -10359,16 +10359,16 @@
         <v>379</v>
       </c>
       <c r="Y46" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="Z46" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="AA46">
-        <v>0.99012440822560344</v>
+        <v>0.99376440697670854</v>
       </c>
       <c r="AB46">
-        <v>181.05251586393737</v>
+        <v>114.31920542701046</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -10433,16 +10433,16 @@
         <v>381</v>
       </c>
       <c r="Y47" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="Z47" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="AA47">
-        <v>0.99593912771817861</v>
+        <v>0.98955368335535221</v>
       </c>
       <c r="AB47">
-        <v>74.449325166725842</v>
+        <v>191.51580515187584</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -10507,16 +10507,16 @@
         <v>383</v>
       </c>
       <c r="Y48" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Z48" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA48">
-        <v>0.99002892693938738</v>
+        <v>0.99310639001954748</v>
       </c>
       <c r="AB48">
-        <v>182.80300611123195</v>
+        <v>126.38284964163027</v>
       </c>
     </row>
     <row r="49" spans="2:28">
@@ -10581,16 +10581,16 @@
         <v>385</v>
       </c>
       <c r="Y49" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
       <c r="Z49" t="s">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="AA49">
-        <v>0.98656930418149524</v>
+        <v>0.99732773592901214</v>
       </c>
       <c r="AB49">
-        <v>246.22942333925477</v>
+        <v>48.991507968111527</v>
       </c>
     </row>
     <row r="50" spans="2:28">
@@ -10655,16 +10655,16 @@
         <v>387</v>
       </c>
       <c r="Y50" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="Z50" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="AA50">
-        <v>0.99786910267543361</v>
+        <v>0.9949180004872078</v>
       </c>
       <c r="AB50">
-        <v>39.066450950384784</v>
+        <v>93.1699910678566</v>
       </c>
     </row>
     <row r="51" spans="2:28">
@@ -10729,16 +10729,16 @@
         <v>389</v>
       </c>
       <c r="Y51" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="Z51" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="AA51">
-        <v>0.99670581568863215</v>
+        <v>0.97445949249159303</v>
       </c>
       <c r="AB51">
-        <v>60.393379041744041</v>
+        <v>468.24263765412724</v>
       </c>
     </row>
     <row r="52" spans="2:28">
@@ -10803,16 +10803,16 @@
         <v>391</v>
       </c>
       <c r="Y52" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Z52" t="s">
         <v>422</v>
       </c>
       <c r="AA52">
-        <v>0.99618977432187161</v>
+        <v>0.99209119567036697</v>
       </c>
       <c r="AB52">
-        <v>69.854137432352857</v>
+        <v>144.9947460432729</v>
       </c>
     </row>
   </sheetData>
@@ -10821,7 +10821,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92C55880-511A-4579-A61C-32A5647C5195}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D31543E-2D23-47B6-A8B8-B595C0A61C98}">
   <dimension ref="B9:M36"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10894,7 +10894,7 @@
         <v>509</v>
       </c>
       <c r="K11" t="s">
-        <v>477</v>
+        <v>502</v>
       </c>
       <c r="L11">
         <v>17.70363598691813</v>
@@ -10929,7 +10929,7 @@
         <v>511</v>
       </c>
       <c r="K12" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="L12">
         <v>4.4260814914900113</v>
@@ -10964,7 +10964,7 @@
         <v>513</v>
       </c>
       <c r="K13" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="L13">
         <v>1.4474450718314593</v>
@@ -10999,7 +10999,7 @@
         <v>515</v>
       </c>
       <c r="K14" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="L14">
         <v>0.72343972786861466</v>
@@ -11034,7 +11034,7 @@
         <v>517</v>
       </c>
       <c r="K15" t="s">
-        <v>491</v>
+        <v>507</v>
       </c>
       <c r="L15">
         <v>6.1480723913003441</v>
@@ -11069,7 +11069,7 @@
         <v>519</v>
       </c>
       <c r="K16" t="s">
-        <v>497</v>
+        <v>476</v>
       </c>
       <c r="L16">
         <v>10.863405343516137</v>
@@ -11139,7 +11139,7 @@
         <v>523</v>
       </c>
       <c r="K18" t="s">
-        <v>496</v>
+        <v>475</v>
       </c>
       <c r="L18">
         <v>14.076384733126485</v>
@@ -11174,7 +11174,7 @@
         <v>525</v>
       </c>
       <c r="K19" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="L19">
         <v>8.4464635782414437</v>
@@ -11209,7 +11209,7 @@
         <v>527</v>
       </c>
       <c r="K20" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="L20">
         <v>21.642919120596623</v>
@@ -11244,7 +11244,7 @@
         <v>529</v>
       </c>
       <c r="K21" t="s">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="L21">
         <v>27.990342065627281</v>
@@ -11279,7 +11279,7 @@
         <v>531</v>
       </c>
       <c r="K22" t="s">
-        <v>478</v>
+        <v>503</v>
       </c>
       <c r="L22">
         <v>89.646947909520648</v>
@@ -11314,7 +11314,7 @@
         <v>533</v>
       </c>
       <c r="K23" t="s">
-        <v>479</v>
+        <v>508</v>
       </c>
       <c r="L23">
         <v>62.125729513990208</v>
@@ -11349,7 +11349,7 @@
         <v>535</v>
       </c>
       <c r="K24" t="s">
-        <v>508</v>
+        <v>479</v>
       </c>
       <c r="L24">
         <v>37.346593817425763</v>
@@ -11384,7 +11384,7 @@
         <v>537</v>
       </c>
       <c r="K25" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="L25">
         <v>11.360303706048013</v>
@@ -11419,7 +11419,7 @@
         <v>539</v>
       </c>
       <c r="K26" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="L26">
         <v>0.75965369142186157</v>
@@ -11454,7 +11454,7 @@
         <v>541</v>
       </c>
       <c r="K27" t="s">
-        <v>475</v>
+        <v>496</v>
       </c>
       <c r="L27">
         <v>15.846874964737275</v>
@@ -11489,7 +11489,7 @@
         <v>543</v>
       </c>
       <c r="K28" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="L28">
         <v>1.3566074605859626</v>
@@ -11559,7 +11559,7 @@
         <v>547</v>
       </c>
       <c r="K30" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="L30">
         <v>2.2634839908418303</v>
@@ -11594,7 +11594,7 @@
         <v>549</v>
       </c>
       <c r="K31" t="s">
-        <v>506</v>
+        <v>477</v>
       </c>
       <c r="L31">
         <v>0.68595098302878366</v>
@@ -11629,7 +11629,7 @@
         <v>551</v>
       </c>
       <c r="K32" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="L32">
         <v>2.6902491287740404</v>
@@ -11664,7 +11664,7 @@
         <v>553</v>
       </c>
       <c r="K33" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="L33">
         <v>0.89338876270880585</v>
@@ -11699,7 +11699,7 @@
         <v>555</v>
       </c>
       <c r="K34" t="s">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="L34">
         <v>13.787970947079426</v>
@@ -11734,7 +11734,7 @@
         <v>557</v>
       </c>
       <c r="K35" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="L35">
         <v>2.7269163699155112</v>
@@ -11784,7 +11784,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B7F46ED-2C65-4E58-8630-374529F0AF5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70744A5B-577E-4C2C-9892-7B636B786625}">
   <dimension ref="B9:S128"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
